--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.29072916282666</v>
+        <v>13.69724348895933</v>
       </c>
       <c r="D2" t="n">
-        <v>83.33847720749849</v>
+        <v>13.5425025462185</v>
       </c>
       <c r="E2" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F2" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.95809039593112</v>
+        <v>3.080689689338807</v>
       </c>
       <c r="D3" t="n">
-        <v>19.00323749436897</v>
+        <v>3.088026092834957</v>
       </c>
       <c r="E3" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F3" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.73115227370529</v>
+        <v>5.48131224447711</v>
       </c>
       <c r="D4" t="n">
-        <v>33.68494297079022</v>
+        <v>5.473803232753411</v>
       </c>
       <c r="E4" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F4" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.230491421227105</v>
+        <v>1.174954855949405</v>
       </c>
       <c r="D5" t="n">
-        <v>7.183810655165425</v>
+        <v>1.167369231464382</v>
       </c>
       <c r="E5" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F5" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.210270422990293</v>
+        <v>1.334168943735923</v>
       </c>
       <c r="D6" t="n">
-        <v>8.207127906492351</v>
+        <v>1.333658284805007</v>
       </c>
       <c r="E6" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F6" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.3219035873982</v>
+        <v>2.327309332952207</v>
       </c>
       <c r="D7" t="n">
-        <v>14.34700848460233</v>
+        <v>2.331388878747878</v>
       </c>
       <c r="E7" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F7" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.9416337218621</v>
+        <v>3.890515479802592</v>
       </c>
       <c r="D8" t="n">
-        <v>25.28448584186052</v>
+        <v>4.108728949302335</v>
       </c>
       <c r="E8" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F8" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.47959718004456</v>
+        <v>2.352934541757242</v>
       </c>
       <c r="D9" t="n">
-        <v>14.71975678848823</v>
+        <v>2.391960478129337</v>
       </c>
       <c r="E9" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F9" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.98334695902338</v>
+        <v>2.434793880841299</v>
       </c>
       <c r="D10" t="n">
-        <v>16.33927475453893</v>
+        <v>2.655132147612576</v>
       </c>
       <c r="E10" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F10" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.9349513519496</v>
+        <v>4.53942959469181</v>
       </c>
       <c r="D11" t="n">
-        <v>28.31090370977568</v>
+        <v>4.600521852838548</v>
       </c>
       <c r="E11" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F11" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.17242364332861</v>
+        <v>2.628018842040899</v>
       </c>
       <c r="D12" t="n">
-        <v>16.9852805551526</v>
+        <v>2.760108090212297</v>
       </c>
       <c r="E12" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F12" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.325560727807032</v>
+        <v>1.515403618268643</v>
       </c>
       <c r="D13" t="n">
-        <v>8.413056417933944</v>
+        <v>1.367121667914266</v>
       </c>
       <c r="E13" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F13" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.461668551581087</v>
+        <v>1.212521139631927</v>
       </c>
       <c r="D14" t="n">
-        <v>7.500131270778636</v>
+        <v>1.218771331501528</v>
       </c>
       <c r="E14" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F14" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.43915055837516</v>
+        <v>2.996361965735964</v>
       </c>
       <c r="D15" t="n">
-        <v>17.26370799491312</v>
+        <v>2.805352549173382</v>
       </c>
       <c r="E15" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F15" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.22240113661751</v>
+        <v>2.473640184700346</v>
       </c>
       <c r="D16" t="n">
-        <v>15.347014710153</v>
+        <v>2.493889890399862</v>
       </c>
       <c r="E16" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F16" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>17.67486537083558</v>
+        <v>2.872165622760782</v>
       </c>
       <c r="D17" t="n">
-        <v>16.61147200577269</v>
+        <v>2.699364200938063</v>
       </c>
       <c r="E17" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F17" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.14007424114671</v>
+        <v>4.89776206418634</v>
       </c>
       <c r="D18" t="n">
-        <v>28.88926065105114</v>
+        <v>4.69450485579581</v>
       </c>
       <c r="E18" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F18" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.10934666383291</v>
+        <v>3.917768832872849</v>
       </c>
       <c r="D19" t="n">
-        <v>22.90866467072182</v>
+        <v>3.722658008992296</v>
       </c>
       <c r="E19" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F19" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.48140812214717</v>
+        <v>3.815728819848915</v>
       </c>
       <c r="D20" t="n">
-        <v>23.9187002455134</v>
+        <v>3.886788789895928</v>
       </c>
       <c r="E20" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F20" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.63516849950692</v>
+        <v>4.490714881169874</v>
       </c>
       <c r="D21" t="n">
-        <v>26.72391382652218</v>
+        <v>4.342635996809855</v>
       </c>
       <c r="E21" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F21" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>17.65741753643326</v>
+        <v>2.869330349670405</v>
       </c>
       <c r="D22" t="n">
-        <v>17.50410808135627</v>
+        <v>2.844417563220394</v>
       </c>
       <c r="E22" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F22" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>32.00265115411491</v>
+        <v>5.200430812543674</v>
       </c>
       <c r="D23" t="n">
-        <v>30.67265209005018</v>
+        <v>4.984305964633154</v>
       </c>
       <c r="E23" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F23" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>24.31590339154645</v>
+        <v>3.951334301126299</v>
       </c>
       <c r="D24" t="n">
-        <v>24.48267927458027</v>
+        <v>3.978435382119295</v>
       </c>
       <c r="E24" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F24" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>18.0051531437043</v>
+        <v>2.925837385851949</v>
       </c>
       <c r="D25" t="n">
-        <v>18.16181845901949</v>
+        <v>2.951295499590667</v>
       </c>
       <c r="E25" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F25" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>8.20555224147059</v>
+        <v>1.333402239238971</v>
       </c>
       <c r="D26" t="n">
-        <v>8.629190706840212</v>
+        <v>1.402243489861535</v>
       </c>
       <c r="E26" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F26" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>15.73943886079022</v>
+        <v>2.557658814878411</v>
       </c>
       <c r="D27" t="n">
-        <v>15.41584058578873</v>
+        <v>2.505074095190669</v>
       </c>
       <c r="E27" t="n">
-        <v>14.65471771649122</v>
+        <v>2.381391628929822</v>
       </c>
       <c r="F27" t="n">
-        <v>14.44020865834781</v>
+        <v>2.34653390698152</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
